--- a/rendusrncp/cahier_recettes.xlsx
+++ b/rendusrncp/cahier_recettes.xlsx
@@ -872,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="28.42578125" defaultRowHeight="23.25"/>
   <cols>
     <col width="7.28515625" customWidth="1" style="32" min="1" max="1"/>
@@ -5195,320 +5195,379 @@
     <row r="83" ht="75" customHeight="1">
       <c r="B83" s="34" t="inlineStr">
         <is>
+          <t>CONT-03</t>
+        </is>
+      </c>
+      <c r="C83" s="35" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="D83" s="35" t="inlineStr">
+        <is>
+          <t>Fonctionnel</t>
+        </is>
+      </c>
+      <c r="E83" s="36" t="inlineStr">
+        <is>
+          <t>Moyenne</t>
+        </is>
+      </c>
+      <c r="F83" s="35" t="inlineStr">
+        <is>
+          <t>Validation manuelle du canal support en conditions réelles</t>
+        </is>
+      </c>
+      <c r="G83" s="35" t="inlineStr">
+        <is>
+          <t>Formulaire /contact accessible en production, adresse support configurée (support@gauthierfitness.fr)</t>
+        </is>
+      </c>
+      <c r="H83" s="35" t="inlineStr">
+        <is>
+          <t>1. Un testeur externe soumet un message réel via /contact sur gauthierfitness.fr
+2. Le candidat consulte le message reçu sur la boîte support
+3. Le candidat répond au testeur</t>
+        </is>
+      </c>
+      <c r="I83" s="35" t="inlineStr">
+        <is>
+          <t>Le message arrive dans la boîte support configurée, avec Reply-To pointant vers l'expéditeur réel. La réponse du candidat parvient bien au testeur.</t>
+        </is>
+      </c>
+      <c r="J83" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K83" s="35" t="inlineStr">
+        <is>
+          <t>Manuel — testé le 09/07/2026 (2 itérations)</t>
+        </is>
+      </c>
+      <c r="L83" s="35" t="inlineStr">
+        <is>
+          <t>Testeur externe : Guillaume F. Question réelle sur le poids de la veste coupe-vent (produit hommes-vestes-veste-coupe-vent-900). 1re itération via gauthierfitness.help@gmail.com, réponse en 25 min. 2e itération après migration vers support@gauthierfitness.fr (OVH Email Pro), réponse en ~20 min avec signature pro complète. Preuves : preuves_recettes/contact-support-question-produit-recue.png et contact-support-question-produit-reponse.png. Alimente Bloc 4, C4.3.3 (collaboration support).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="75" customHeight="1">
+      <c r="B84" s="34" t="inlineStr">
+        <is>
           <t>SEC-01</t>
         </is>
       </c>
-      <c r="C83" s="35" t="inlineStr">
+      <c r="C84" s="35" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="D83" s="35" t="inlineStr">
+      <c r="D84" s="35" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="E83" s="36" t="inlineStr">
+      <c r="E84" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F83" s="35" t="inlineStr">
+      <c r="F84" s="35" t="inlineStr">
         <is>
           <t>Header HSTS présent sur prod HTTPS</t>
         </is>
       </c>
-      <c r="G83" s="35" t="inlineStr">
+      <c r="G84" s="35" t="inlineStr">
         <is>
           <t>Site servi en HTTPS via Nginx</t>
         </is>
       </c>
-      <c r="H83" s="35" t="inlineStr">
+      <c r="H84" s="35" t="inlineStr">
         <is>
           <t>1. curl -I https://gauthierfitness.fr | grep -i strict</t>
         </is>
       </c>
-      <c r="I83" s="35" t="inlineStr">
+      <c r="I84" s="35" t="inlineStr">
         <is>
           <t>Header Strict-Transport-Security retourné avec max-age et includeSubDomains.</t>
         </is>
       </c>
-      <c r="J83" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K83" s="35" t="inlineStr">
+      <c r="J84" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K84" s="35" t="inlineStr">
         <is>
           <t>Manuel curl</t>
         </is>
       </c>
-      <c r="L83" s="35" t="inlineStr">
+      <c r="L84" s="35" t="inlineStr">
         <is>
           <t>Correctif (infra/nginx/prod.conf + staging.conf, commits 6db4d70/15a5853) déployé et vérifié en direct le 08/07/2026 : curl -I sur https://gauthierfitness.fr et https://staging.gauthierfitness.fr renvoient Strict-Transport-Security: max-age=31536000; includeSubDomains. Le commentaire précédent ("non commité, non déployé") était obsolète. Capture : preuves_recettes/sec01-sec02-headers-hsts-csp-prod.png.</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="75" customHeight="1">
-      <c r="B84" s="38" t="inlineStr">
+    <row r="85" ht="75" customHeight="1">
+      <c r="B85" s="38" t="inlineStr">
         <is>
           <t>SEC-02</t>
         </is>
       </c>
-      <c r="C84" s="39" t="inlineStr">
+      <c r="C85" s="39" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="D84" s="39" t="inlineStr">
+      <c r="D85" s="39" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="E84" s="39" t="inlineStr">
+      <c r="E85" s="39" t="inlineStr">
         <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F84" s="39" t="inlineStr">
+      <c r="F85" s="39" t="inlineStr">
         <is>
           <t>CSP empêche scripts inline non autorisés</t>
         </is>
       </c>
-      <c r="G84" s="39" t="inlineStr">
+      <c r="G85" s="39" t="inlineStr">
         <is>
           <t>Prod en HTTPS</t>
         </is>
       </c>
-      <c r="H84" s="39" t="inlineStr">
+      <c r="H85" s="39" t="inlineStr">
         <is>
           <t>1. Inspecter Content-Security-Policy retourné</t>
         </is>
       </c>
-      <c r="I84" s="39" t="inlineStr">
+      <c r="I85" s="39" t="inlineStr">
         <is>
           <t>CSP présent autorisant uniquement self + js.stripe.com.</t>
         </is>
       </c>
-      <c r="J84" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K84" s="39" t="inlineStr">
+      <c r="J85" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K85" s="39" t="inlineStr">
         <is>
           <t>Manuel curl</t>
         </is>
       </c>
-      <c r="L84" s="39" t="inlineStr">
+      <c r="L85" s="39" t="inlineStr">
         <is>
           <t>Correctif déployé et vérifié en direct le 08/07/2026 : curl -I sur prod et staging renvoient un header Content-Security-Policy restrictif (self + js.stripe.com + Sentry). Même correctif que SEC-01, même commit. Capture : preuves_recettes/sec01-sec02-headers-hsts-csp-prod.png.</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="75" customHeight="1">
-      <c r="B85" s="34" t="inlineStr">
+    <row r="86" ht="75" customHeight="1">
+      <c r="B86" s="34" t="inlineStr">
         <is>
           <t>SEC-03</t>
         </is>
       </c>
-      <c r="C85" s="35" t="inlineStr">
+      <c r="C86" s="35" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="D85" s="35" t="inlineStr">
+      <c r="D86" s="35" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="E85" s="36" t="inlineStr">
+      <c r="E86" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F85" s="35" t="inlineStr">
+      <c r="F86" s="35" t="inlineStr">
         <is>
           <t>Audit composer sans vulnérabilité critique</t>
         </is>
       </c>
-      <c r="G85" s="35" t="inlineStr">
+      <c r="G86" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H85" s="35" t="inlineStr">
+      <c r="H86" s="35" t="inlineStr">
         <is>
           <t>1. composer audit (sur backend)</t>
         </is>
       </c>
-      <c r="I85" s="35" t="inlineStr">
+      <c r="I86" s="35" t="inlineStr">
         <is>
           <t>Aucune vulnérabilité critique ou high.</t>
         </is>
       </c>
-      <c r="J85" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K85" s="35" t="inlineStr">
+      <c r="J86" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K86" s="35" t="inlineStr">
         <is>
           <t>Manuel composer audit</t>
         </is>
       </c>
-      <c r="L85" s="35" t="inlineStr">
+      <c r="L86" s="35" t="inlineStr">
         <is>
           <t>composer audit exécuté le 06/07/2026 sur backend — aucune vulnérabilité.</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="75" customHeight="1">
-      <c r="B86" s="38" t="inlineStr">
+    <row r="87" ht="75" customHeight="1">
+      <c r="B87" s="38" t="inlineStr">
         <is>
           <t>SEC-04</t>
         </is>
       </c>
-      <c r="C86" s="39" t="inlineStr">
+      <c r="C87" s="39" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="D86" s="39" t="inlineStr">
+      <c r="D87" s="39" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="E86" s="36" t="inlineStr">
+      <c r="E87" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F86" s="39" t="inlineStr">
+      <c r="F87" s="39" t="inlineStr">
         <is>
           <t>Audit npm sans vulnérabilité critique</t>
         </is>
       </c>
-      <c r="G86" s="39" t="inlineStr">
+      <c r="G87" s="39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H86" s="39" t="inlineStr">
+      <c r="H87" s="39" t="inlineStr">
         <is>
           <t>1. npm audit (sur frontend)</t>
         </is>
       </c>
-      <c r="I86" s="39" t="inlineStr">
+      <c r="I87" s="39" t="inlineStr">
         <is>
           <t>Aucune vulnérabilité critique ou high.</t>
         </is>
       </c>
-      <c r="J86" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K86" s="39" t="inlineStr">
+      <c r="J87" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K87" s="39" t="inlineStr">
         <is>
           <t>Manuel npm audit</t>
         </is>
       </c>
-      <c r="L86" s="39" t="inlineStr">
+      <c r="L87" s="39" t="inlineStr">
         <is>
           <t>npm audit exécuté le 06/07/2026 sur frontend — aucune vulnérabilité.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="75" customHeight="1">
-      <c r="B87" s="34" t="inlineStr">
+    <row r="88" ht="75" customHeight="1">
+      <c r="B88" s="34" t="inlineStr">
         <is>
           <t>SEC-05</t>
         </is>
       </c>
-      <c r="C87" s="35" t="inlineStr">
+      <c r="C88" s="35" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="D87" s="35" t="inlineStr">
+      <c r="D88" s="35" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="E87" s="36" t="inlineStr">
+      <c r="E88" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F87" s="35" t="inlineStr">
+      <c r="F88" s="35" t="inlineStr">
         <is>
           <t>MySQL non exposé depuis Internet</t>
         </is>
       </c>
-      <c r="G87" s="35" t="inlineStr">
+      <c r="G88" s="35" t="inlineStr">
         <is>
           <t>VPS prod</t>
         </is>
       </c>
-      <c r="H87" s="35" t="inlineStr">
+      <c r="H88" s="35" t="inlineStr">
         <is>
           <t>1. nmap -p 3306 &lt;ip_vps_prod&gt;</t>
         </is>
       </c>
-      <c r="I87" s="35" t="inlineStr">
+      <c r="I88" s="35" t="inlineStr">
         <is>
           <t>Port 3306 filtré ou fermé (jamais ouvert).</t>
         </is>
       </c>
-      <c r="J87" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K87" s="35" t="inlineStr">
+      <c r="J88" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K88" s="35" t="inlineStr">
         <is>
           <t>Manuel nmap</t>
         </is>
       </c>
-      <c r="L87" s="35" t="inlineStr">
+      <c r="L88" s="35" t="inlineStr">
         <is>
           <t>Test de connexion TCP externe sur le port 3306 le 06/07/2026 — fermé sur prod (51.38.234.197) et staging (51.210.15.118).</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="75" customHeight="1">
-      <c r="B88" s="38" t="inlineStr">
+    <row r="89" ht="75" customHeight="1">
+      <c r="B89" s="38" t="inlineStr">
         <is>
           <t>A11Y-01</t>
         </is>
       </c>
-      <c r="C88" s="39" t="inlineStr">
+      <c r="C89" s="39" t="inlineStr">
         <is>
           <t>Accessibilité</t>
         </is>
       </c>
-      <c r="D88" s="39" t="inlineStr">
+      <c r="D89" s="39" t="inlineStr">
         <is>
           <t>Accessibilité</t>
         </is>
       </c>
-      <c r="E88" s="39" t="inlineStr">
+      <c r="E89" s="39" t="inlineStr">
         <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F88" s="39" t="inlineStr">
+      <c r="F89" s="39" t="inlineStr">
         <is>
           <t>Navigation clavier sur le parcours d'achat</t>
         </is>
       </c>
-      <c r="G88" s="39" t="inlineStr">
+      <c r="G89" s="39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H88" s="39" t="inlineStr">
+      <c r="H89" s="39" t="inlineStr">
         <is>
           <t>1. Home → Tab → focus sur premier item de nav
 2. Continuer Tab → traverser Header, Hero, catalogue
@@ -5516,967 +5575,950 @@
 4. Ajouter au panier via Espace/Entrée</t>
         </is>
       </c>
-      <c r="I88" s="39" t="inlineStr">
+      <c r="I89" s="39" t="inlineStr">
         <is>
           <t>Tous les éléments interactifs sont accessibles au clavier. Focus visible. Ordre logique.</t>
         </is>
       </c>
-      <c r="J88" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K88" s="39" t="inlineStr">
+      <c r="J89" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K89" s="39" t="inlineStr">
         <is>
           <t>Manuel</t>
         </is>
       </c>
-      <c r="L88" s="39" t="inlineStr">
+      <c r="L89" s="39" t="inlineStr">
         <is>
           <t>Testé le 06/07/2026 sur staging (parcours Home → catalogue → fiche produit → ajout panier, entièrement au clavier). Focus visible à chaque étape, ordre logique respecté. Preuve : capture vidéo de l'écran + captures d'écran (à joindre dans preuves_recettes/).</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="75" customHeight="1">
-      <c r="B89" s="34" t="inlineStr">
+    <row r="90" ht="75" customHeight="1">
+      <c r="B90" s="34" t="inlineStr">
         <is>
           <t>A11Y-02</t>
         </is>
       </c>
-      <c r="C89" s="35" t="inlineStr">
+      <c r="C90" s="35" t="inlineStr">
         <is>
           <t>Accessibilité</t>
         </is>
       </c>
-      <c r="D89" s="35" t="inlineStr">
+      <c r="D90" s="35" t="inlineStr">
         <is>
           <t>Accessibilité</t>
         </is>
       </c>
-      <c r="E89" s="35" t="inlineStr">
+      <c r="E90" s="35" t="inlineStr">
         <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F89" s="35" t="inlineStr">
+      <c r="F90" s="35" t="inlineStr">
         <is>
           <t>Score Lighthouse Accessibility ≥ 90 sur Home</t>
         </is>
       </c>
-      <c r="G89" s="35" t="inlineStr">
+      <c r="G90" s="35" t="inlineStr">
         <is>
           <t>Build prod servi</t>
         </is>
       </c>
-      <c r="H89" s="35" t="inlineStr">
+      <c r="H90" s="35" t="inlineStr">
         <is>
           <t>1. Chrome DevTools → Lighthouse → Accessibility</t>
         </is>
       </c>
-      <c r="I89" s="35" t="inlineStr">
+      <c r="I90" s="35" t="inlineStr">
         <is>
           <t>Score ≥ 90.</t>
         </is>
       </c>
-      <c r="J89" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K89" s="35" t="inlineStr">
+      <c r="J90" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K90" s="35" t="inlineStr">
         <is>
           <t>Manuel Lighthouse</t>
         </is>
       </c>
-      <c r="L89" s="35" t="inlineStr">
+      <c r="L90" s="35" t="inlineStr">
         <is>
           <t>Audit Lighthouse Home après correctifs (RNCP-Lighthouse-GF29, 05/07/2026) — score Accessibility 100 (≥ 90 requis).</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="75" customHeight="1">
-      <c r="B90" s="38" t="inlineStr">
+    <row r="91" ht="75" customHeight="1">
+      <c r="B91" s="38" t="inlineStr">
         <is>
           <t>A11Y-03</t>
         </is>
       </c>
-      <c r="C90" s="39" t="inlineStr">
+      <c r="C91" s="39" t="inlineStr">
         <is>
           <t>Accessibilité</t>
         </is>
       </c>
-      <c r="D90" s="39" t="inlineStr">
+      <c r="D91" s="39" t="inlineStr">
         <is>
           <t>Accessibilité</t>
         </is>
       </c>
-      <c r="E90" s="39" t="inlineStr">
+      <c r="E91" s="39" t="inlineStr">
         <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F90" s="39" t="inlineStr">
+      <c r="F91" s="39" t="inlineStr">
         <is>
           <t>Alt présent sur toutes les images de produit</t>
         </is>
       </c>
-      <c r="G90" s="39" t="inlineStr">
+      <c r="G91" s="39" t="inlineStr">
         <is>
           <t>Page catalogue chargée</t>
         </is>
       </c>
-      <c r="H90" s="39" t="inlineStr">
+      <c r="H91" s="39" t="inlineStr">
         <is>
           <t>1. Inspecter DOM, vérifier &lt;img alt="..."&gt;</t>
         </is>
       </c>
-      <c r="I90" s="39" t="inlineStr">
+      <c r="I91" s="39" t="inlineStr">
         <is>
           <t>Chaque image produit a un alt non vide. Images décoratives ont alt="".</t>
         </is>
       </c>
-      <c r="J90" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K90" s="39" t="inlineStr">
+      <c r="J91" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K91" s="39" t="inlineStr">
         <is>
           <t>Manuel inspecteur</t>
         </is>
       </c>
-      <c r="L90" s="39" t="inlineStr">
+      <c r="L91" s="39" t="inlineStr">
         <is>
           <t>Audit Lighthouse Home après correctifs — audit « image-alt » à 100 %. Vérifié sur Home uniquement ; produit/panier/checkout restent à vérifier si besoin.</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="75" customHeight="1">
-      <c r="B91" s="34" t="inlineStr">
+    <row r="92" ht="75" customHeight="1">
+      <c r="B92" s="34" t="inlineStr">
         <is>
           <t>UI-01</t>
         </is>
       </c>
-      <c r="C91" s="35" t="inlineStr">
+      <c r="C92" s="35" t="inlineStr">
         <is>
           <t>Frontend UI</t>
         </is>
       </c>
-      <c r="D91" s="35" t="inlineStr">
+      <c r="D92" s="35" t="inlineStr">
         <is>
           <t>Structurel</t>
         </is>
       </c>
-      <c r="E91" s="35" t="inlineStr">
+      <c r="E92" s="35" t="inlineStr">
         <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F91" s="35" t="inlineStr">
+      <c r="F92" s="35" t="inlineStr">
         <is>
           <t>axios intercepteur attache Bearer token</t>
         </is>
       </c>
-      <c r="G91" s="35" t="inlineStr">
+      <c r="G92" s="35" t="inlineStr">
         <is>
           <t>Token en localStorage</t>
         </is>
       </c>
-      <c r="H91" s="35" t="inlineStr">
+      <c r="H92" s="35" t="inlineStr">
         <is>
           <t>1. Appeler n'importe quel endpoint</t>
         </is>
       </c>
-      <c r="I91" s="35" t="inlineStr">
+      <c r="I92" s="35" t="inlineStr">
         <is>
           <t>Header Authorization: Bearer &lt;token&gt; ajouté à chaque requête.</t>
         </is>
       </c>
-      <c r="J91" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K91" s="35" t="inlineStr">
+      <c r="J92" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K92" s="35" t="inlineStr">
         <is>
           <t>Jest axios.test.js::attaches Bearer token</t>
         </is>
       </c>
-      <c r="L91" s="35" t="inlineStr">
-        <is>
-          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="75" customHeight="1">
-      <c r="B92" s="38" t="inlineStr">
+      <c r="L92" s="35" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="75" customHeight="1">
+      <c r="B93" s="38" t="inlineStr">
         <is>
           <t>UI-02</t>
         </is>
       </c>
-      <c r="C92" s="39" t="inlineStr">
+      <c r="C93" s="39" t="inlineStr">
         <is>
           <t>Frontend UI</t>
         </is>
       </c>
-      <c r="D92" s="39" t="inlineStr">
+      <c r="D93" s="39" t="inlineStr">
         <is>
           <t>Structurel</t>
         </is>
       </c>
-      <c r="E92" s="39" t="inlineStr">
+      <c r="E93" s="39" t="inlineStr">
         <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F92" s="39" t="inlineStr">
+      <c r="F93" s="39" t="inlineStr">
         <is>
           <t>axios 401 purge le token automatiquement</t>
         </is>
       </c>
-      <c r="G92" s="39" t="inlineStr">
+      <c r="G93" s="39" t="inlineStr">
         <is>
           <t>Token expired en localStorage</t>
         </is>
       </c>
-      <c r="H92" s="39" t="inlineStr">
+      <c r="H93" s="39" t="inlineStr">
         <is>
           <t>1. Endpoint renvoie 401</t>
         </is>
       </c>
-      <c r="I92" s="39" t="inlineStr">
+      <c r="I93" s="39" t="inlineStr">
         <is>
           <t>localStorage.token supprimé. User doit re-login.</t>
         </is>
       </c>
-      <c r="J92" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K92" s="39" t="inlineStr">
+      <c r="J93" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K93" s="39" t="inlineStr">
         <is>
           <t>Jest axios.test.js::removes token from localStorage on 401</t>
         </is>
       </c>
-      <c r="L92" s="39" t="inlineStr">
-        <is>
-          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="75" customHeight="1">
-      <c r="B93" s="34" t="inlineStr">
+      <c r="L93" s="39" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="46.5" customHeight="1">
+      <c r="B94" s="34" t="inlineStr">
         <is>
           <t>UI-03</t>
         </is>
       </c>
-      <c r="C93" s="35" t="inlineStr">
+      <c r="C94" s="35" t="inlineStr">
         <is>
           <t>Frontend UI</t>
         </is>
       </c>
-      <c r="D93" s="35" t="inlineStr">
+      <c r="D94" s="35" t="inlineStr">
         <is>
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="E93" s="36" t="inlineStr">
+      <c r="E94" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F93" s="35" t="inlineStr">
+      <c r="F94" s="35" t="inlineStr">
         <is>
           <t>AuthProvider login persiste user + token</t>
         </is>
       </c>
-      <c r="G93" s="35" t="inlineStr">
+      <c r="G94" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H93" s="35" t="inlineStr">
+      <c r="H94" s="35" t="inlineStr">
         <is>
           <t>1. login("alice@a.fr", "secret")
 2. Inspecter localStorage</t>
         </is>
       </c>
-      <c r="I93" s="35" t="inlineStr">
+      <c r="I94" s="35" t="inlineStr">
         <is>
           <t>token + user (JSON) en localStorage. Context expose isAuthenticated=true.</t>
         </is>
       </c>
-      <c r="J93" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K93" s="35" t="inlineStr">
+      <c r="J94" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K94" s="35" t="inlineStr">
         <is>
           <t>Jest auth.test.jsx::login stores token + user</t>
         </is>
       </c>
-      <c r="L93" s="35" t="inlineStr">
-        <is>
-          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="46.5" customHeight="1">
-      <c r="B94" s="38" t="inlineStr">
+      <c r="L94" s="35" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="46.5" customHeight="1">
+      <c r="B95" s="38" t="inlineStr">
         <is>
           <t>UI-04</t>
         </is>
       </c>
-      <c r="C94" s="39" t="inlineStr">
+      <c r="C95" s="39" t="inlineStr">
         <is>
           <t>Frontend UI</t>
         </is>
       </c>
-      <c r="D94" s="39" t="inlineStr">
+      <c r="D95" s="39" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="E94" s="36" t="inlineStr">
+      <c r="E95" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F94" s="39" t="inlineStr">
+      <c r="F95" s="39" t="inlineStr">
         <is>
           <t>AuthProvider 401 sur /me → purge tout</t>
         </is>
       </c>
-      <c r="G94" s="39" t="inlineStr">
+      <c r="G95" s="39" t="inlineStr">
         <is>
           <t>Token expired</t>
         </is>
       </c>
-      <c r="H94" s="39" t="inlineStr">
+      <c r="H95" s="39" t="inlineStr">
         <is>
           <t>1. Bootstrap au mount, /me renvoie 401</t>
         </is>
       </c>
-      <c r="I94" s="39" t="inlineStr">
+      <c r="I95" s="39" t="inlineStr">
         <is>
           <t>Token + user purgés du localStorage. isAuthenticated=false.</t>
         </is>
       </c>
-      <c r="J94" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K94" s="39" t="inlineStr">
+      <c r="J95" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K95" s="39" t="inlineStr">
         <is>
           <t>Jest auth.test.jsx::bootstrap clears token on /me returning 401</t>
         </is>
       </c>
-      <c r="L94" s="39" t="inlineStr">
-        <is>
-          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="46.5" customHeight="1">
-      <c r="B95" s="34" t="inlineStr">
+      <c r="L95" s="39" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="34" t="inlineStr">
         <is>
           <t>UI-05</t>
         </is>
       </c>
-      <c r="C95" s="35" t="inlineStr">
+      <c r="C96" s="35" t="inlineStr">
         <is>
           <t>Frontend UI</t>
         </is>
       </c>
-      <c r="D95" s="35" t="inlineStr">
+      <c r="D96" s="35" t="inlineStr">
         <is>
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="E95" s="35" t="inlineStr">
+      <c r="E96" s="35" t="inlineStr">
         <is>
           <t>Moyenne</t>
         </is>
       </c>
-      <c r="F95" s="35" t="inlineStr">
+      <c r="F96" s="35" t="inlineStr">
         <is>
           <t>AuthProvider 500 ne purge pas (backend down)</t>
         </is>
       </c>
-      <c r="G95" s="35" t="inlineStr">
+      <c r="G96" s="35" t="inlineStr">
         <is>
           <t>Token valide, backend down</t>
         </is>
       </c>
-      <c r="H95" s="35" t="inlineStr">
+      <c r="H96" s="35" t="inlineStr">
         <is>
           <t>1. Bootstrap, /me renvoie 500</t>
         </is>
       </c>
-      <c r="I95" s="35" t="inlineStr">
+      <c r="I96" s="35" t="inlineStr">
         <is>
           <t>Token + user CONSERVÉS. User reste connecté visuellement.</t>
         </is>
       </c>
-      <c r="J95" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K95" s="35" t="inlineStr">
+      <c r="J96" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K96" s="35" t="inlineStr">
         <is>
           <t>Jest auth.test.jsx::bootstrap keeps token when /me errors with 500</t>
         </is>
       </c>
-      <c r="L95" s="35" t="inlineStr">
-        <is>
-          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="38" t="inlineStr">
+      <c r="L96" s="35" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="46.5" customHeight="1">
+      <c r="B97" s="38" t="inlineStr">
         <is>
           <t>UI-06</t>
         </is>
       </c>
-      <c r="C96" s="39" t="inlineStr">
+      <c r="C97" s="39" t="inlineStr">
         <is>
           <t>Frontend UI</t>
         </is>
       </c>
-      <c r="D96" s="39" t="inlineStr">
+      <c r="D97" s="39" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="E96" s="36" t="inlineStr">
+      <c r="E97" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F96" s="39" t="inlineStr">
+      <c r="F97" s="39" t="inlineStr">
         <is>
           <t>ProtectedRoute redirige /login si pas auth</t>
         </is>
       </c>
-      <c r="G96" s="39" t="inlineStr">
+      <c r="G97" s="39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H96" s="39" t="inlineStr">
+      <c r="H97" s="39" t="inlineStr">
         <is>
           <t>1. Naviguer /dashboard sans token</t>
         </is>
       </c>
-      <c r="I96" s="39" t="inlineStr">
+      <c r="I97" s="39" t="inlineStr">
         <is>
           <t>Redirection vers /login.</t>
         </is>
       </c>
-      <c r="J96" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K96" s="39" t="inlineStr">
+      <c r="J97" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K97" s="39" t="inlineStr">
         <is>
           <t>Jest ProtectedRoutes.test.jsx + Cypress admin.cy.js</t>
         </is>
       </c>
-      <c r="L96" s="39" t="inlineStr">
+      <c r="L97" s="39" t="inlineStr">
         <is>
           <t>Suite Jest rejouée le 08/07/2026 : ProtectedRoute.test.jsx 3/3 vert (39 tests Jest frontend au total, tous verts). Capture : preuves_recettes/ui06-protectedroute-test.png.</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="46.5" customHeight="1">
-      <c r="B97" s="34" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="34" t="inlineStr">
         <is>
           <t>UI-07</t>
         </is>
       </c>
-      <c r="C97" s="35" t="inlineStr">
+      <c r="C98" s="35" t="inlineStr">
         <is>
           <t>Frontend UI</t>
         </is>
       </c>
-      <c r="D97" s="35" t="inlineStr">
+      <c r="D98" s="35" t="inlineStr">
         <is>
           <t>Sécurité</t>
         </is>
       </c>
-      <c r="E97" s="36" t="inlineStr">
+      <c r="E98" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F97" s="35" t="inlineStr">
+      <c r="F98" s="35" t="inlineStr">
         <is>
           <t>AdminRoute affiche un message d'accès refusé si connecté mais pas admin</t>
         </is>
       </c>
-      <c r="G97" s="35" t="inlineStr">
+      <c r="G98" s="35" t="inlineStr">
         <is>
           <t>User customer connecté</t>
         </is>
       </c>
-      <c r="H97" s="35" t="inlineStr">
+      <c r="H98" s="35" t="inlineStr">
         <is>
           <t>1. Naviguer /admin</t>
         </is>
       </c>
-      <c r="I97" s="35" t="inlineStr">
+      <c r="I98" s="35" t="inlineStr">
         <is>
           <t>Message "Accès refusé" affiché. Pas de redirection, pas d'affichage du panel admin.</t>
         </is>
       </c>
-      <c r="J97" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K97" s="35" t="inlineStr">
+      <c r="J98" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K98" s="35" t="inlineStr">
         <is>
           <t>Jest AdminRoutes.test.jsx::shows an access-denied message when authenticated but not admin</t>
         </is>
       </c>
-      <c r="L97" s="35" t="inlineStr">
-        <is>
-          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="38" t="inlineStr">
+      <c r="L98" s="35" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="63" customHeight="1">
+      <c r="B99" s="38" t="inlineStr">
         <is>
           <t>UI-08</t>
         </is>
       </c>
-      <c r="C98" s="39" t="inlineStr">
+      <c r="C99" s="39" t="inlineStr">
         <is>
           <t>Frontend UI</t>
         </is>
       </c>
-      <c r="D98" s="39" t="inlineStr">
+      <c r="D99" s="39" t="inlineStr">
         <is>
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="E98" s="39" t="inlineStr">
+      <c r="E99" s="39" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
       </c>
-      <c r="F98" s="39" t="inlineStr">
+      <c r="F99" s="39" t="inlineStr">
         <is>
           <t>ProductCard affiche prix au format X.XX €</t>
         </is>
       </c>
-      <c r="G98" s="39" t="inlineStr">
+      <c r="G99" s="39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H98" s="39" t="inlineStr">
+      <c r="H99" s="39" t="inlineStr">
         <is>
           <t>1. Rendre ProductCard avec price_ttc=29.9</t>
         </is>
       </c>
-      <c r="I98" s="39" t="inlineStr">
+      <c r="I99" s="39" t="inlineStr">
         <is>
           <t>Affiche "29.90 €" (2 décimales).</t>
         </is>
       </c>
-      <c r="J98" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K98" s="39" t="inlineStr">
+      <c r="J99" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K99" s="39" t="inlineStr">
         <is>
           <t>Jest ProductCard.test.jsx::renders product name and price</t>
         </is>
       </c>
-      <c r="L98" s="39" t="inlineStr">
-        <is>
-          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="63" customHeight="1">
-      <c r="B99" s="34" t="inlineStr">
+      <c r="L99" s="39" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="34" t="inlineStr">
         <is>
           <t>UI-09</t>
         </is>
       </c>
-      <c r="C99" s="35" t="inlineStr">
+      <c r="C100" s="35" t="inlineStr">
         <is>
           <t>Frontend UI</t>
         </is>
       </c>
-      <c r="D99" s="35" t="inlineStr">
+      <c r="D100" s="35" t="inlineStr">
         <is>
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="E99" s="35" t="inlineStr">
+      <c r="E100" s="35" t="inlineStr">
         <is>
           <t>Basse</t>
         </is>
       </c>
-      <c r="F99" s="35" t="inlineStr">
+      <c r="F100" s="35" t="inlineStr">
         <is>
           <t>ProductCard change d'image au hover</t>
         </is>
       </c>
-      <c r="G99" s="35" t="inlineStr">
+      <c r="G100" s="35" t="inlineStr">
         <is>
           <t>Produit avec main_image et hover_image</t>
         </is>
       </c>
-      <c r="H99" s="35" t="inlineStr">
+      <c r="H100" s="35" t="inlineStr">
         <is>
           <t>1. mouseEnter sur la carte</t>
         </is>
       </c>
-      <c r="I99" s="35" t="inlineStr">
+      <c r="I100" s="35" t="inlineStr">
         <is>
           <t>Le src de l'image passe de main_image à hover_image.</t>
         </is>
       </c>
-      <c r="J99" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K99" s="35" t="inlineStr">
+      <c r="J100" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K100" s="35" t="inlineStr">
         <is>
           <t>Jest ProductCard.test.jsx::shows hover image on mouse enter</t>
         </is>
       </c>
-      <c r="L99" s="35" t="inlineStr">
-        <is>
-          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="38" t="inlineStr">
+      <c r="L100" s="35" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="46.5" customHeight="1">
+      <c r="B101" s="38" t="inlineStr">
         <is>
           <t>INFRA-01</t>
         </is>
       </c>
-      <c r="C100" s="39" t="inlineStr">
+      <c r="C101" s="39" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D100" s="39" t="inlineStr">
+      <c r="D101" s="39" t="inlineStr">
         <is>
           <t>Fonctionnel</t>
         </is>
       </c>
-      <c r="E100" s="36" t="inlineStr">
+      <c r="E101" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F100" s="39" t="inlineStr">
+      <c r="F101" s="39" t="inlineStr">
         <is>
           <t>Health check /api/health renvoie 200</t>
         </is>
       </c>
-      <c r="G100" s="39" t="inlineStr">
+      <c r="G101" s="39" t="inlineStr">
         <is>
           <t>Backend démarré</t>
         </is>
       </c>
-      <c r="H100" s="39" t="inlineStr">
+      <c r="H101" s="39" t="inlineStr">
         <is>
           <t>1. GET /api/health</t>
         </is>
       </c>
-      <c r="I100" s="39" t="inlineStr">
+      <c r="I101" s="39" t="inlineStr">
         <is>
           <t>Réponse 200 {status:"ok", env:"production"}.</t>
         </is>
       </c>
-      <c r="J100" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K100" s="39" t="inlineStr">
+      <c r="J101" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K101" s="39" t="inlineStr">
         <is>
           <t>PHPUnit HealthTest</t>
         </is>
       </c>
-      <c r="L100" s="39" t="inlineStr">
-        <is>
-          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="46.5" customHeight="1">
-      <c r="B101" s="34" t="inlineStr">
+      <c r="L101" s="39" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="46.5" customHeight="1">
+      <c r="B102" s="34" t="inlineStr">
         <is>
           <t>INFRA-02</t>
         </is>
       </c>
-      <c r="C101" s="35" t="inlineStr">
+      <c r="C102" s="35" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D101" s="35" t="inlineStr">
+      <c r="D102" s="35" t="inlineStr">
         <is>
           <t>Structurel</t>
         </is>
       </c>
-      <c r="E101" s="36" t="inlineStr">
+      <c r="E102" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F101" s="35" t="inlineStr">
+      <c r="F102" s="35" t="inlineStr">
         <is>
           <t>CI backend verte sur PR</t>
         </is>
       </c>
-      <c r="G101" s="35" t="inlineStr">
+      <c r="G102" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H101" s="35" t="inlineStr">
+      <c r="H102" s="35" t="inlineStr">
         <is>
           <t>1. Push sur GF{n}
 2. Ouvrir PR vers develop</t>
         </is>
       </c>
-      <c r="I101" s="35" t="inlineStr">
+      <c r="I102" s="35" t="inlineStr">
         <is>
           <t>Workflow CI : PHPUnit + Pint + Build image + Trigger infra → tous verts.</t>
         </is>
       </c>
-      <c r="J101" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K101" s="35" t="inlineStr">
+      <c r="J102" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K102" s="35" t="inlineStr">
         <is>
           <t>GitHub Actions backend ci-cd.yml</t>
         </is>
       </c>
-      <c r="L101" s="35" t="inlineStr">
+      <c r="L102" s="35" t="inlineStr">
         <is>
           <t>CI backend vérifiée verte le 08/07/2026 : sur push develop/main (ex. run GitHub Actions #28949610914) et sur pull request (ex. run #28868839895, PR GF31-V1GF-Ready -&gt; develop). ci-cd.yml se déclenche bien sur push ET pull_request vers main/develop. Capture : preuves_recettes/infra02-ci-backend-pr.png.</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="46.5" customHeight="1">
-      <c r="B102" s="38" t="inlineStr">
+    <row r="103" ht="69.75" customHeight="1">
+      <c r="B103" s="38" t="inlineStr">
         <is>
           <t>INFRA-03</t>
         </is>
       </c>
-      <c r="C102" s="39" t="inlineStr">
+      <c r="C103" s="39" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D102" s="39" t="inlineStr">
+      <c r="D103" s="39" t="inlineStr">
         <is>
           <t>Structurel</t>
         </is>
       </c>
-      <c r="E102" s="36" t="inlineStr">
+      <c r="E103" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F102" s="39" t="inlineStr">
+      <c r="F103" s="39" t="inlineStr">
         <is>
           <t>CI frontend verte sur PR</t>
         </is>
       </c>
-      <c r="G102" s="39" t="inlineStr">
+      <c r="G103" s="39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H102" s="39" t="inlineStr">
+      <c r="H103" s="39" t="inlineStr">
         <is>
           <t>1. Push + PR</t>
         </is>
       </c>
-      <c r="I102" s="39" t="inlineStr">
+      <c r="I103" s="39" t="inlineStr">
         <is>
           <t>Workflow CI : ESLint + Build Vite + Jest + Build image → tous verts.</t>
         </is>
       </c>
-      <c r="J102" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K102" s="39" t="inlineStr">
+      <c r="J103" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K103" s="39" t="inlineStr">
         <is>
           <t>GitHub Actions frontend ci-cd.yml</t>
         </is>
       </c>
-      <c r="L102" s="39" t="inlineStr">
+      <c r="L103" s="39" t="inlineStr">
         <is>
           <t>CI frontend vérifiée verte le 08/07/2026 : sur push develop/main (ex. run #28925409791) et sur pull request (ex. run Dependabot #28925617135). ci-cd.yml se déclenche bien sur push ET pull_request vers main/develop. Capture : preuves_recettes/infra03-ci-frontend-pr.png.</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="69.75" customHeight="1">
-      <c r="B103" s="34" t="inlineStr">
+    <row r="104" ht="46.5" customHeight="1">
+      <c r="B104" s="34" t="inlineStr">
         <is>
           <t>INFRA-04</t>
         </is>
       </c>
-      <c r="C103" s="35" t="inlineStr">
+      <c r="C104" s="35" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D103" s="35" t="inlineStr">
+      <c r="D104" s="35" t="inlineStr">
         <is>
           <t>Structurel</t>
         </is>
       </c>
-      <c r="E103" s="36" t="inlineStr">
+      <c r="E104" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F103" s="35" t="inlineStr">
+      <c r="F104" s="35" t="inlineStr">
         <is>
           <t>Pipeline complet : staging → e2e → prod</t>
         </is>
       </c>
-      <c r="G103" s="35" t="inlineStr">
+      <c r="G104" s="35" t="inlineStr">
         <is>
           <t>Push sur develop puis main</t>
         </is>
       </c>
-      <c r="H103" s="35" t="inlineStr">
+      <c r="H104" s="35" t="inlineStr">
         <is>
           <t>1. Push develop → staging auto deploy + e2e Cypress
 2. Merge dans main → trigger manuel prod</t>
         </is>
       </c>
-      <c r="I103" s="35" t="inlineStr">
+      <c r="I104" s="35" t="inlineStr">
         <is>
           <t>Staging green. E2E Cypress green. Prod deploy manuel OK avec health check 200 à la fin.</t>
         </is>
       </c>
-      <c r="J103" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K103" s="35" t="inlineStr">
+      <c r="J104" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K104" s="35" t="inlineStr">
         <is>
           <t>GitHub Actions infra deploy.yml</t>
         </is>
       </c>
-      <c r="L103" s="35" t="inlineStr">
+      <c r="L104" s="35" t="inlineStr">
         <is>
           <t>Pipeline complet vérifié le 08/07/2026 : run infra #28949784465 (staging, déclenché par repository_dispatch après CI backend/frontend) -&gt; Staging Deployment vert (48s) -&gt; Tests E2E Cypress vert (1m24s). Déploiement prod le plus récent : run #28883415233 (workflow_dispatch manuel, 07/07/2026, vert, 42s). Health check confirmé en direct le 08/07/2026 : GET https://gauthierfitness.fr/api/health -&gt; 200 {"status":"ok"}. Capture : preuves_recettes/infra04-pipeline-staging-e2e.png.</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="46.5" customHeight="1">
-      <c r="B104" s="34" t="inlineStr">
+    <row r="105">
+      <c r="B105" s="34" t="inlineStr">
         <is>
           <t>INFRA-05</t>
         </is>
       </c>
-      <c r="C104" s="35" t="inlineStr">
+      <c r="C105" s="35" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D104" s="35" t="inlineStr">
+      <c r="D105" s="35" t="inlineStr">
         <is>
           <t>Structurel</t>
         </is>
       </c>
-      <c r="E104" s="36" t="inlineStr">
+      <c r="E105" s="36" t="inlineStr">
         <is>
           <t>Haute</t>
         </is>
       </c>
-      <c r="F104" s="35" t="inlineStr">
+      <c r="F105" s="35" t="inlineStr">
         <is>
           <t>Pipeline complet :  production</t>
         </is>
       </c>
-      <c r="G104" s="35" t="inlineStr">
+      <c r="G105" s="35" t="inlineStr">
         <is>
           <t>Déclenchement manuel validé</t>
         </is>
       </c>
-      <c r="H104" s="35" t="inlineStr">
+      <c r="H105" s="35" t="inlineStr">
         <is>
           <t>Merge dans main → trigger manuel prod</t>
         </is>
       </c>
-      <c r="I104" s="35" t="inlineStr">
+      <c r="I105" s="35" t="inlineStr">
         <is>
           <t>Prod deploy manuel OK avec health check 200 à la fin.</t>
         </is>
       </c>
-      <c r="J104" s="37" t="inlineStr">
-        <is>
-          <t>Passé</t>
-        </is>
-      </c>
-      <c r="K104" s="35" t="inlineStr">
+      <c r="J105" s="37" t="inlineStr">
+        <is>
+          <t>Passé</t>
+        </is>
+      </c>
+      <c r="K105" s="35" t="inlineStr">
         <is>
           <t>GitHub Actions infra deploy.yml</t>
         </is>
       </c>
-      <c r="L104" s="35" t="inlineStr">
+      <c r="L105" s="35" t="inlineStr">
         <is>
           <t>Pipeline complet vérifié le 08/07/2026 : run infra #28973278625 (commit 2504e06, Production Deployment 52s, approuvé manuellement par Charles). Capture : preuves_recettes/infra05-pipeline-production.png.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="42" t="inlineStr">
+    <row r="109">
+      <c r="B109" s="42" t="inlineStr">
         <is>
           <t>Total scénarios : 95</t>
         </is>
       </c>
-      <c r="C108" s="43" t="n"/>
-      <c r="D108" s="44" t="n"/>
-      <c r="E108" s="41" t="n"/>
-      <c r="F108" s="41" t="n"/>
-      <c r="G108" s="41" t="n"/>
-      <c r="H108" s="41" t="n"/>
-      <c r="I108" s="41" t="n"/>
-      <c r="J108" s="41" t="n"/>
-      <c r="K108" s="41" t="n"/>
-      <c r="L108" s="41" t="n"/>
-    </row>
-    <row r="109">
-      <c r="B109" s="45" t="inlineStr">
-        <is>
-          <t>Légende statut : "À jouer" (gris) / "Passé" (vert) / "Échec" (rouge)</t>
-        </is>
-      </c>
-      <c r="C109" s="41" t="n"/>
-      <c r="D109" s="46" t="n"/>
+      <c r="C109" s="43" t="n"/>
+      <c r="D109" s="44" t="n"/>
       <c r="E109" s="41" t="n"/>
       <c r="F109" s="41" t="n"/>
       <c r="G109" s="41" t="n"/>
@@ -6489,7 +6531,7 @@
     <row r="110">
       <c r="B110" s="45" t="inlineStr">
         <is>
-          <t>Mettre à jour la colonne Statut au fil des exécutions.</t>
+          <t>Légende statut : "À jouer" (gris) / "Passé" (vert) / "Échec" (rouge)</t>
         </is>
       </c>
       <c r="C110" s="41" t="n"/>
@@ -6504,9 +6546,26 @@
       <c r="L110" s="41" t="n"/>
     </row>
     <row r="111">
-      <c r="B111" s="47" t="n"/>
-      <c r="C111" s="40" t="n"/>
-      <c r="D111" s="48" t="n"/>
+      <c r="B111" s="45" t="inlineStr">
+        <is>
+          <t>Mettre à jour la colonne Statut au fil des exécutions.</t>
+        </is>
+      </c>
+      <c r="C111" s="41" t="n"/>
+      <c r="D111" s="46" t="n"/>
+      <c r="E111" s="41" t="n"/>
+      <c r="F111" s="41" t="n"/>
+      <c r="G111" s="41" t="n"/>
+      <c r="H111" s="41" t="n"/>
+      <c r="I111" s="41" t="n"/>
+      <c r="J111" s="41" t="n"/>
+      <c r="K111" s="41" t="n"/>
+      <c r="L111" s="41" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="47" t="n"/>
+      <c r="C112" s="40" t="n"/>
+      <c r="D112" s="48" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="B9:L102"/>
@@ -6542,7 +6601,6 @@
       <c r="C1" s="20" t="n"/>
       <c r="D1" s="21" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="23" t="inlineStr">
         <is>
@@ -6690,11 +6748,9 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
+        <v>3</v>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
         <is>
@@ -6722,7 +6778,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -6755,8 +6811,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
@@ -6794,7 +6848,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32">
@@ -6807,8 +6861,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
         <is>
@@ -6836,7 +6888,7 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38">
@@ -6859,7 +6911,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
@@ -6867,7 +6918,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/rendusrncp/cahier_recettes.xlsx
+++ b/rendusrncp/cahier_recettes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\Desktop\gauthierfitness\rendusrncp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59313143-0C25-4D5D-A6C1-2D82A9173B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A61A0AB-5DB2-46AE-A1AB-2A8CB2DE0251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,9 +98,6 @@
     <t>PHPUnit AuthTest::test_user_can_register</t>
   </si>
   <si>
-    <t>Suite complète rejouée le 06/07/2026 : 164 tests PHPUnit backend + 39 tests Jest frontend, tous verts.</t>
-  </si>
-  <si>
     <t>AUTH-02</t>
   </si>
   <si>
@@ -144,9 +141,6 @@
     <t>PHPUnit AuthTest::test_user_can_login + Cypress auth.cy.js</t>
   </si>
   <si>
-    <t>Suite complète rejouée le 08/07/2026 : 162 tests PHPUnit backend + 39 tests Jest frontend, tous verts (AuthTest::test_user_can_login confirmé). Capture : preuves_recettes/auth03-adm03-adm07-adm11-backend-tests.png.</t>
-  </si>
-  <si>
     <t>AUTH-04</t>
   </si>
   <si>
@@ -996,9 +990,6 @@
 Carte 2 : authentification échouée, paiement refusé, commande reste non payée.</t>
   </si>
   <si>
-    <t>Manuel — Stripe Test Mode (cartes 4000002500003155 et 4000008400001629)</t>
-  </si>
-  <si>
     <t>Testé le 06-07/07/2026 en staging (Stripe test mode). Carte 4000002500003155 : challenge 3DS puis Complete → paiement succeeded, commande Confirmée. Carte 4000008400001629 : challenge puis Fail → carte refusée, commande reste non payée. Bug annexe trouvé et corrigé au passage (voir FICHES_INCIDENTS.md fiche 6) : webhook payment_intent.payment_failed non écouté sur le endpoint staging → ajouté, retest confirmé (commande passe bien en failed).</t>
   </si>
   <si>
@@ -1110,9 +1101,6 @@
     <t>PHPUnit AdminOrderControllerTest::test_admin_can_view_stats + Cypress admin.cy.js</t>
   </si>
   <si>
-    <t>Suite complète rejouée le 08/07/2026 : AdminOrderControllerTest::test_admin_can_view_stats vert (162 tests PHPUnit backend au total, tous verts). Capture : preuves_recettes/auth03-adm03-adm07-adm11-backend-tests.png.</t>
-  </si>
-  <si>
     <t>ADM-04</t>
   </si>
   <si>
@@ -1185,9 +1173,6 @@
     <t>PHPUnit AdminOrderControllerTest::test_admin_can_list_orders + Cypress admin.cy.js</t>
   </si>
   <si>
-    <t>Suite complète rejouée le 08/07/2026 : AdminOrderControllerTest::test_admin_can_list_orders vert (162 tests PHPUnit backend au total, tous verts). Capture : preuves_recettes/auth03-adm03-adm07-adm11-backend-tests.png.</t>
-  </si>
-  <si>
     <t>ADM-08</t>
   </si>
   <si>
@@ -1258,9 +1243,6 @@
   </si>
   <si>
     <t>PHPUnit AdminStockControllerTest::test_admin_can_add_stock + Cypress admin-stock.cy.js</t>
-  </si>
-  <si>
-    <t>Suite complète rejouée le 08/07/2026 : AdminStockControllerTest::test_admin_can_add_stock vert (162 tests PHPUnit backend au total, tous verts). Capture : preuves_recettes/auth03-adm03-adm07-adm11-backend-tests.png.</t>
   </si>
   <si>
     <t>ADM-12</t>
@@ -1497,9 +1479,6 @@
     <t>Manuel composer audit</t>
   </si>
   <si>
-    <t>composer audit exécuté le 06/07/2026 sur backend — aucune vulnérabilité.</t>
-  </si>
-  <si>
     <t>SEC-04</t>
   </si>
   <si>
@@ -1512,9 +1491,6 @@
     <t>Manuel npm audit</t>
   </si>
   <si>
-    <t>npm audit exécuté le 06/07/2026 sur frontend — aucune vulnérabilité.</t>
-  </si>
-  <si>
     <t>SEC-05</t>
   </si>
   <si>
@@ -1531,9 +1507,6 @@
   </si>
   <si>
     <t>Manuel nmap</t>
-  </si>
-  <si>
-    <t>Test de connexion TCP externe sur le port 3306 le 06/07/2026 — fermé sur prod (51.38.234.197) et staging (51.210.15.118).</t>
   </si>
   <si>
     <t>A11Y-01</t>
@@ -1578,9 +1551,6 @@
     <t>Manuel Lighthouse</t>
   </si>
   <si>
-    <t>Audit Lighthouse Home après correctifs (RNCP-Lighthouse-GF29, 05/07/2026) — score Accessibility 100 (≥ 90 requis).</t>
-  </si>
-  <si>
     <t>A11Y-03</t>
   </si>
   <si>
@@ -1597,9 +1567,6 @@
   </si>
   <si>
     <t>Manuel inspecteur</t>
-  </si>
-  <si>
-    <t>Audit Lighthouse Home après correctifs — audit « image-alt » à 100 %. Vérifié sur Home uniquement ; produit/panier/checkout restent à vérifier si besoin.</t>
   </si>
   <si>
     <t>UI-01</t>
@@ -1708,9 +1675,6 @@
     <t>Jest ProtectedRoutes.test.jsx + Cypress admin.cy.js</t>
   </si>
   <si>
-    <t>Suite Jest rejouée le 08/07/2026 : ProtectedRoute.test.jsx 3/3 vert (39 tests Jest frontend au total, tous verts). Capture : preuves_recettes/ui06-protectedroute-test.png.</t>
-  </si>
-  <si>
     <t>UI-07</t>
   </si>
   <si>
@@ -1959,6 +1923,42 @@
   <si>
     <t>Mise à jour : la colonne "Statut" doit refléter la dernière exécution
 Date et tester à mentionner en "Commentaire" si nécessaire</t>
+  </si>
+  <si>
+    <t>Suite complète rejouée le 13/07/2026 : 166 tests PHPUnit backend + 40 tests Jest frontend, tous verts.</t>
+  </si>
+  <si>
+    <t>Suite complète rejouée le 13/07/2026 : 166 tests PHPUnit backend + 40 tests Jest frontend, tous verts (AuthTest::test_user_can_login confirmé). Capture : preuves_recettes/auth03-adm03-adm07-adm11-backend-tests.png.</t>
+  </si>
+  <si>
+    <t>Manuel - Stripe Test Mode (cartes 4000002500003155 et 4000008400001629)</t>
+  </si>
+  <si>
+    <t>Suite complète rejouée le 13/07/2026 : AdminOrderControllerTest::test_admin_can_view_stats vert (166 tests PHPUnit backend au total, tous verts). Capture : preuves_recettes/auth03-adm03-adm07-adm11-backend-tests.png.</t>
+  </si>
+  <si>
+    <t>Suite complète rejouée le 13/07/2026 : AdminOrderControllerTest::test_admin_can_list_orders vert (166 tests PHPUnit backend au total, tous verts). Capture : preuves_recettes/auth03-adm03-adm07-adm11-backend-tests.png.</t>
+  </si>
+  <si>
+    <t>Suite complète rejouée le 13/07/2026 : AdminStockControllerTest::test_admin_can_add_stock vert (166 tests PHPUnit backend au total, tous verts). Capture : preuves_recettes/auth03-adm03-adm07-adm11-backend-tests.png.</t>
+  </si>
+  <si>
+    <t>npm audit exécuté le 13/07/2026 sur frontend - aucune vulnérabilité.</t>
+  </si>
+  <si>
+    <t>composer audit exécuté le 13/07/2026 sur backend - aucune vulnérabilité.</t>
+  </si>
+  <si>
+    <t>Test de connexion TCP externe sur le port 3306 le 06/07/2026 - fermé sur prod (51.38.234.197) et staging (51.210.15.118).</t>
+  </si>
+  <si>
+    <t>Audit Lighthouse Home après correctifs (RNCP-Lighthouse-GF29, 05/07/2026) - score Accessibility 100 (≥ 90 requis).</t>
+  </si>
+  <si>
+    <t>Audit Lighthouse Home après correctifs - audit « image-alt » à 100 %. Vérifié sur Home uniquement ; produit/panier/checkout restent à vérifier si besoin.</t>
+  </si>
+  <si>
+    <t>Suite Jest rejouée le 13/07/2026 : ProtectedRoute.test.jsx 3/3 vert (40 tests Jest frontend au total, tous verts). Capture : preuves_recettes/ui06-protectedroute-test.png.</t>
   </si>
 </sst>
 </file>
@@ -2210,7 +2210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2242,25 +2242,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2284,23 +2266,8 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2320,7 +2287,37 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2638,38 +2635,38 @@
     <col min="9" max="9" width="119.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" style="1" customWidth="1"/>
     <col min="11" max="11" width="72.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="92.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="103.28515625" style="1" customWidth="1"/>
     <col min="13" max="13" width="28.42578125" style="1" customWidth="1"/>
     <col min="14" max="16384" width="28.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
     </row>
     <row r="3" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
     </row>
     <row r="4" spans="2:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
@@ -2685,32 +2682,32 @@
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
     </row>
     <row r="7" spans="2:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:12" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2780,47 +2777,47 @@
         <v>22</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="J10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="9" t="s">
+      <c r="L10" s="5" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>14</v>
@@ -2832,65 +2829,65 @@
         <v>16</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="J11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="L11" s="5" t="s">
-        <v>37</v>
+        <v>622</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="I12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="J12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>23</v>
+      <c r="L12" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>14</v>
@@ -2899,33 +2896,33 @@
         <v>15</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="J13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="L13" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>14</v>
@@ -2934,68 +2931,68 @@
         <v>15</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="I14" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="J14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>23</v>
+      <c r="L14" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="I15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="J15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>62</v>
-      </c>
       <c r="L15" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>14</v>
@@ -3007,100 +3004,100 @@
         <v>16</v>
       </c>
       <c r="F16" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="I16" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="J16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>23</v>
+      <c r="L16" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="J17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="L17" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F18" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="I18" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="J18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="I18" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>23</v>
+      <c r="L18" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>14</v>
@@ -3112,68 +3109,68 @@
         <v>16</v>
       </c>
       <c r="F19" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="J19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>86</v>
-      </c>
       <c r="L19" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="I20" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="J20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="I20" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>23</v>
+      <c r="L20" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>15</v>
@@ -3182,138 +3179,138 @@
         <v>16</v>
       </c>
       <c r="F21" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="I21" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="J21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="L21" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F22" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="I22" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="J22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="I22" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>23</v>
+      <c r="L22" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="J23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="L23" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="24" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="9" t="s">
+      <c r="F24" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="G24" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="H24" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="I24" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="J24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I24" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>23</v>
+      <c r="L24" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="25" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>15</v>
@@ -3322,68 +3319,68 @@
         <v>16</v>
       </c>
       <c r="F25" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="I25" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="J25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="L25" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F26" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="I26" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="G26" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" s="9" t="s">
+      <c r="J26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="I26" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>23</v>
+      <c r="L26" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="27" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>15</v>
@@ -3392,33 +3389,33 @@
         <v>16</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="I27" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="J27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>137</v>
-      </c>
       <c r="L27" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>15</v>
@@ -3427,33 +3424,33 @@
         <v>16</v>
       </c>
       <c r="F28" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="H28" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="I28" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="J28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="I28" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>23</v>
+      <c r="L28" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="29" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>15</v>
@@ -3462,278 +3459,278 @@
         <v>16</v>
       </c>
       <c r="F29" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="I29" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="J29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>149</v>
-      </c>
       <c r="L29" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="30" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="I30" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="J30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="I30" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K30" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>23</v>
+      <c r="L30" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="31" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="I31" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="J31" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>161</v>
-      </c>
       <c r="L31" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="32" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F32" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="H32" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="I32" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="J32" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="I32" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>23</v>
+      <c r="L32" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="33" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F33" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H33" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="I33" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="J33" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>173</v>
-      </c>
       <c r="L33" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="34" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F34" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H34" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="I34" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="J34" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I34" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>23</v>
+      <c r="L34" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="35" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F35" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="I35" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="J35" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K35" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>185</v>
-      </c>
       <c r="L35" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="36" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F36" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="I36" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="J36" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="H36" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="L36" s="9" t="s">
-        <v>23</v>
+      <c r="L36" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="37" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>15</v>
@@ -3742,348 +3739,348 @@
         <v>16</v>
       </c>
       <c r="F37" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="I37" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="J37" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="I37" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>197</v>
-      </c>
       <c r="L37" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="38" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F38" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="H38" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="I38" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="J38" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K38" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="I38" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K38" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="L38" s="9" t="s">
-        <v>23</v>
+      <c r="L38" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="39" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F39" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="I39" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="J39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K39" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>209</v>
-      </c>
       <c r="L39" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="40" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F40" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="H40" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="I40" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="J40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K40" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="I40" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K40" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="L40" s="9" t="s">
-        <v>23</v>
+      <c r="L40" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F41" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>219</v>
-      </c>
       <c r="L41" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="42" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F42" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="H42" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="I42" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="J42" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K42" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="I42" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K42" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="L42" s="9" t="s">
-        <v>23</v>
+      <c r="L42" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="43" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="G43" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" s="5" t="s">
+      <c r="H43" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="I43" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="J43" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K43" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>231</v>
-      </c>
       <c r="L43" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="44" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F44" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="H44" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="I44" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="J44" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K44" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="I44" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K44" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="L44" s="9" t="s">
-        <v>23</v>
+      <c r="L44" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="45" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F45" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="I45" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H45" s="5" t="s">
+      <c r="J45" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>242</v>
-      </c>
       <c r="L45" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="46" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H46" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F46" s="9" t="s">
+      <c r="I46" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="G46" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H46" s="9" t="s">
+      <c r="J46" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K46" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="I46" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="J46" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="L46" s="9" t="s">
-        <v>23</v>
+      <c r="L46" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="47" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>15</v>
@@ -4092,33 +4089,33 @@
         <v>16</v>
       </c>
       <c r="F47" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="H47" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="I47" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="J47" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="I47" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K47" s="5" t="s">
-        <v>254</v>
-      </c>
       <c r="L47" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="48" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>15</v>
@@ -4127,173 +4124,173 @@
         <v>16</v>
       </c>
       <c r="F48" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="I48" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="G48" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="H48" s="9" t="s">
+      <c r="J48" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K48" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="I48" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K48" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="L48" s="9" t="s">
-        <v>23</v>
+      <c r="L48" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="49" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F49" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="I49" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H49" s="5" t="s">
+      <c r="J49" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K49" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="I49" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K49" s="5" t="s">
-        <v>264</v>
-      </c>
       <c r="L49" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="50" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F50" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H50" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="I50" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="J50" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K50" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="I50" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="L50" s="9" t="s">
-        <v>23</v>
+      <c r="L50" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F51" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="H51" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G51" s="5" t="s">
+      <c r="I51" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="H51" s="5" t="s">
+      <c r="J51" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K51" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K51" s="5" t="s">
-        <v>276</v>
-      </c>
       <c r="L51" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F52" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="H52" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="I52" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="H52" s="9" t="s">
+      <c r="J52" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="I52" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="J52" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K52" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="L52" s="9" t="s">
-        <v>23</v>
+      <c r="L52" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="53" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>15</v>
@@ -4302,33 +4299,33 @@
         <v>16</v>
       </c>
       <c r="F53" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="H53" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="G53" s="5" t="s">
+      <c r="I53" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="J53" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K53" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="I53" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>288</v>
-      </c>
       <c r="L53" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="54" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>15</v>
@@ -4337,33 +4334,33 @@
         <v>16</v>
       </c>
       <c r="F54" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="H54" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="I54" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="H54" s="9" t="s">
+      <c r="J54" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K54" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="I54" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="J54" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K54" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="L54" s="9" t="s">
-        <v>23</v>
+      <c r="L54" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>15</v>
@@ -4372,138 +4369,138 @@
         <v>16</v>
       </c>
       <c r="F55" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="H55" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G55" s="5" t="s">
+      <c r="I55" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="H55" s="5" t="s">
+      <c r="J55" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K55" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="I55" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K55" s="5" t="s">
-        <v>300</v>
-      </c>
       <c r="L55" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="56" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F56" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="H56" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="I56" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="H56" s="9" t="s">
+      <c r="J56" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K56" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="I56" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K56" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="L56" s="9" t="s">
-        <v>23</v>
+      <c r="L56" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F57" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I57" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="H57" s="5" t="s">
+      <c r="J57" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K57" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="I57" s="5" t="s">
+      <c r="L57" s="5" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" ht="231.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="J57" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K57" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="L57" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="4" t="s">
-        <v>312</v>
-      </c>
       <c r="C58" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F58" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="H58" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="I58" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="H58" s="5" t="s">
+      <c r="J58" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="L58" s="5" t="s">
         <v>315</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K58" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="L58" s="5" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="59" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="8" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>15</v>
@@ -4512,173 +4509,173 @@
         <v>16</v>
       </c>
       <c r="F59" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="I59" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="J59" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K59" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="H59" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K59" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>23</v>
+      <c r="L59" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="60" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F60" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="I60" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="J60" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K60" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="H60" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K60" s="5" t="s">
-        <v>331</v>
-      </c>
       <c r="L60" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="61" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="8" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F61" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K61" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="G61" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="I61" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>23</v>
+      <c r="L61" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="62" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F62" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="I62" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="J62" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K62" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="H62" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="J62" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K62" s="5" t="s">
-        <v>343</v>
-      </c>
       <c r="L62" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="63" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F63" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K63" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="L63" s="5" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="64" spans="2:12" ht="129.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="H63" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="I63" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K63" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="L63" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="4" t="s">
-        <v>349</v>
-      </c>
       <c r="C64" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>15</v>
@@ -4687,33 +4684,33 @@
         <v>16</v>
       </c>
       <c r="F64" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="I64" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="J64" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K64" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="H64" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="J64" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K64" s="5" t="s">
-        <v>354</v>
-      </c>
       <c r="L64" s="5" t="s">
-        <v>355</v>
+        <v>624</v>
       </c>
     </row>
     <row r="65" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="8" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>15</v>
@@ -4722,103 +4719,103 @@
         <v>16</v>
       </c>
       <c r="F65" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K65" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="G65" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="I65" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K65" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="L65" s="9" t="s">
-        <v>23</v>
+      <c r="L65" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="66" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="I66" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F66" s="5" t="s">
+      <c r="J66" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K66" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G66" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K66" s="5" t="s">
-        <v>367</v>
-      </c>
       <c r="L66" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="67" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="8" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F67" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K67" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="L67" s="5" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" ht="148.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="H67" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="I67" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="J67" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="4" t="s">
-        <v>374</v>
-      </c>
       <c r="C68" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>15</v>
@@ -4827,68 +4824,68 @@
         <v>16</v>
       </c>
       <c r="F68" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K68" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="G68" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K68" s="5" t="s">
-        <v>379</v>
-      </c>
       <c r="L68" s="5" t="s">
-        <v>380</v>
+        <v>625</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="8" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="J69" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K69" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="L69" s="9" t="s">
-        <v>23</v>
+        <v>381</v>
+      </c>
+      <c r="L69" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="70" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>15</v>
@@ -4897,68 +4894,68 @@
         <v>16</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="J70" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="L70" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K71" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="C71" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F71" s="9" t="s">
+      <c r="L71" s="5" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="G71" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="I71" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="J71" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K71" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="L71" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="4" t="s">
-        <v>399</v>
-      </c>
       <c r="C72" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>15</v>
@@ -4967,138 +4964,138 @@
         <v>16</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="J72" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="L72" s="5" t="s">
-        <v>405</v>
+        <v>626</v>
       </c>
     </row>
     <row r="73" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="8" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="J73" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K73" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>23</v>
+        <v>405</v>
+      </c>
+      <c r="L73" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="74" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="4" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="J74" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="L74" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="75" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="8" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="J75" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K75" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>23</v>
+        <v>417</v>
+      </c>
+      <c r="L75" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="76" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="4" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>15</v>
@@ -5107,593 +5104,593 @@
         <v>16</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="I76" s="5" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="J76" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="L76" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="77" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="8" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="J77" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K77" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>23</v>
+        <v>430</v>
+      </c>
+      <c r="L77" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="78" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="4" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="H78" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="I78" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="I78" s="5" t="s">
-        <v>440</v>
-      </c>
       <c r="J78" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="L78" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="79" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="8" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="J79" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K79" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>23</v>
+        <v>440</v>
+      </c>
+      <c r="L79" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="80" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="4" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="J80" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="81" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="8" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="J81" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K81" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="82" spans="2:12" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>451</v>
+      </c>
+      <c r="L81" s="5" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12" ht="208.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="4" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F82" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K82" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="L82" s="5" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12" ht="215.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="G82" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="H82" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="I82" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="J82" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K82" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="L82" s="5" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="83" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="4" t="s">
-        <v>465</v>
-      </c>
       <c r="C83" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F83" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K83" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="L83" s="5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="84" spans="2:12" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="C84" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F84" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="H83" s="5" t="s">
+      <c r="G84" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="I83" s="5" t="s">
+      <c r="H84" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="J83" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K83" s="5" t="s">
+      <c r="I84" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="L83" s="5" t="s">
+      <c r="J84" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K84" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="L84" s="9" t="s">
         <v>471</v>
-      </c>
-    </row>
-    <row r="84" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>474</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="I84" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="J84" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K84" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="L84" s="9" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="85" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="4" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="J85" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L85" s="5" t="s">
-        <v>483</v>
+        <v>628</v>
       </c>
     </row>
     <row r="86" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="8" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="J86" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K86" s="9" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="L86" s="9" t="s">
-        <v>488</v>
+        <v>627</v>
       </c>
     </row>
     <row r="87" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="4" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="J87" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="L87" s="5" t="s">
-        <v>495</v>
+        <v>629</v>
       </c>
     </row>
     <row r="88" spans="2:12" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="8" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="J88" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K88" s="9" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="L88" s="9" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
     </row>
     <row r="89" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="4" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="C89" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H89" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="D89" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>506</v>
-      </c>
       <c r="I89" s="5" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="J89" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="L89" s="5" t="s">
-        <v>509</v>
+        <v>630</v>
       </c>
     </row>
     <row r="90" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="8" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="J90" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K90" s="9" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="L90" s="9" t="s">
-        <v>516</v>
+        <v>631</v>
       </c>
     </row>
     <row r="91" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="4" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="J91" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="L91" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="92" spans="2:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="8" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="C92" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K92" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E92" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="H92" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="I92" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="J92" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K92" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="L92" s="9" t="s">
-        <v>23</v>
+      <c r="L92" s="5" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="93" spans="2:12" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="4" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>15</v>
@@ -5702,243 +5699,243 @@
         <v>16</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="J93" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="L93" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="94" spans="2:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="8" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="J94" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K94" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="L94" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="95" spans="2:12" ht="93" x14ac:dyDescent="0.25">
+        <v>529</v>
+      </c>
+      <c r="L94" s="5" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="95" spans="2:12" ht="69.75" x14ac:dyDescent="0.25">
       <c r="B95" s="4" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="J95" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="L95" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="96" spans="2:12" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="8" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="J96" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K96" s="9" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="L96" s="9" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="97" spans="2:12" ht="139.5" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="97" spans="2:12" ht="69.75" x14ac:dyDescent="0.25">
       <c r="B97" s="4" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="J97" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="L97" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="98" spans="2:12" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="8" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D98" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="J98" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K98" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="L98" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="99" spans="2:12" ht="93" x14ac:dyDescent="0.25">
+        <v>550</v>
+      </c>
+      <c r="L98" s="5" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="99" spans="2:12" ht="46.5" x14ac:dyDescent="0.25">
       <c r="B99" s="4" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="J99" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="L99" s="5" t="s">
-        <v>23</v>
+        <v>621</v>
       </c>
     </row>
     <row r="100" spans="2:12" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="8" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="D100" s="9" t="s">
         <v>15</v>
@@ -5947,170 +5944,170 @@
         <v>16</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="J100" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K100" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="L100" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="101" spans="2:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+        <v>563</v>
+      </c>
+      <c r="L100" s="5" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="101" spans="2:12" ht="165" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="4" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="J101" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="L101" s="5" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
     </row>
     <row r="102" spans="2:12" ht="168" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="8" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="J102" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K102" s="9" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="L102" s="9" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
     </row>
     <row r="103" spans="2:12" ht="202.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="4" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="J103" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="L103" s="5" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
     </row>
     <row r="104" spans="2:12" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="4" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="J104" s="7" t="s">
         <v>21</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
     </row>
     <row r="106" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B106" s="10" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="10"/>
@@ -6125,7 +6122,7 @@
     </row>
     <row r="107" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B107" s="10" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="10"/>
@@ -6140,7 +6137,7 @@
     </row>
     <row r="108" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B108" s="10" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="10"/>
@@ -6166,140 +6163,141 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:C42"/>
+  <dimension ref="B1:C42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="14"/>
-    <col min="2" max="2" width="37.42578125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="34.42578125" style="14" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="14"/>
+    <col min="1" max="1" width="9.140625" style="11"/>
+    <col min="2" max="2" width="37.42578125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="34.42578125" style="11" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="27" t="s">
-        <v>603</v>
-      </c>
-      <c r="C2" s="28"/>
+      <c r="B2" s="29" t="s">
+        <v>591</v>
+      </c>
+      <c r="C2" s="30"/>
     </row>
     <row r="3" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="29" t="s">
-        <v>604</v>
-      </c>
-      <c r="C4" s="30"/>
+      <c r="B4" s="31" t="s">
+        <v>592</v>
+      </c>
+      <c r="C4" s="32"/>
     </row>
     <row r="5" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>605</v>
+      <c r="C5" s="20" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B6" s="32" t="s">
-        <v>338</v>
-      </c>
-      <c r="C6" s="32">
+      <c r="B6" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="C6" s="21">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B7" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="C7" s="32">
+      <c r="B7" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="21">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B8" s="32" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="32">
+      <c r="B8" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B9" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="21">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B9" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9" s="32">
+    <row r="10" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B10" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="21">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B10" s="32" t="s">
-        <v>518</v>
-      </c>
-      <c r="C10" s="32">
+    <row r="11" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B11" s="21" t="s">
+        <v>507</v>
+      </c>
+      <c r="C11" s="21">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B11" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="32">
-        <v>12</v>
-      </c>
-    </row>
     <row r="12" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B12" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="32">
+      <c r="B12" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="21">
         <v>6</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B13" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="32">
+      <c r="B13" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B14" s="32" t="s">
-        <v>425</v>
-      </c>
-      <c r="C14" s="32">
+      <c r="B14" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="C14" s="21">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B15" s="32" t="s">
-        <v>570</v>
-      </c>
-      <c r="C15" s="32">
+      <c r="B15" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="C15" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B16" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="C16" s="32">
+      <c r="B16" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" s="21">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="32" t="s">
-        <v>497</v>
-      </c>
-      <c r="C17" s="32">
+      <c r="B17" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="C17" s="21">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B18" s="32" t="s">
-        <v>448</v>
-      </c>
-      <c r="C18" s="32">
+      <c r="B18" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="C18" s="21">
         <v>3</v>
       </c>
     </row>
@@ -6312,48 +6310,48 @@
       <c r="C20" s="1"/>
     </row>
     <row r="21" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="29" t="s">
-        <v>606</v>
-      </c>
-      <c r="C21" s="30"/>
+      <c r="B21" s="31" t="s">
+        <v>594</v>
+      </c>
+      <c r="C21" s="32"/>
     </row>
     <row r="22" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="31" t="s">
-        <v>605</v>
+      <c r="C22" s="20" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="21">
         <v>47</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B24" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="32">
+      <c r="B24" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="21">
         <v>38</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B25" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="C25" s="32">
+      <c r="B25" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="21">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B26" s="32" t="s">
-        <v>497</v>
-      </c>
-      <c r="C26" s="32">
+      <c r="B26" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="C26" s="21">
         <v>3</v>
       </c>
     </row>
@@ -6366,40 +6364,40 @@
       <c r="C28" s="1"/>
     </row>
     <row r="29" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="29" t="s">
-        <v>607</v>
-      </c>
-      <c r="C29" s="30"/>
+      <c r="B29" s="31" t="s">
+        <v>595</v>
+      </c>
+      <c r="C29" s="32"/>
     </row>
     <row r="30" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="31" t="s">
-        <v>605</v>
+      <c r="C30" s="20" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B31" s="33" t="s">
+      <c r="B31" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="21">
         <v>59</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B32" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="32">
+      <c r="B32" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="21">
         <v>33</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B33" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" s="32">
+      <c r="B33" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" s="21">
         <v>4</v>
       </c>
     </row>
@@ -6412,40 +6410,40 @@
       <c r="C35" s="1"/>
     </row>
     <row r="36" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="29" t="s">
-        <v>608</v>
-      </c>
-      <c r="C36" s="30"/>
+      <c r="B36" s="31" t="s">
+        <v>596</v>
+      </c>
+      <c r="C36" s="32"/>
     </row>
     <row r="37" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="31" t="s">
+      <c r="B37" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="31" t="s">
-        <v>605</v>
+      <c r="C37" s="20" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B38" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C38" s="34">
+      <c r="B38" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="23">
         <v>96</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B39" s="35" t="s">
-        <v>609</v>
-      </c>
-      <c r="C39" s="35">
+      <c r="B39" s="24" t="s">
+        <v>597</v>
+      </c>
+      <c r="C39" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B40" s="36" t="s">
-        <v>610</v>
-      </c>
-      <c r="C40" s="36">
+      <c r="B40" s="25" t="s">
+        <v>598</v>
+      </c>
+      <c r="C40" s="25">
         <v>0</v>
       </c>
     </row>
@@ -6454,10 +6452,10 @@
       <c r="C41" s="1"/>
     </row>
     <row r="42" spans="2:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="37" t="s">
-        <v>611</v>
-      </c>
-      <c r="C42" s="37">
+      <c r="B42" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="C42" s="19">
         <v>96</v>
       </c>
     </row>
@@ -6478,164 +6476,164 @@
   <dimension ref="B1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="21" style="15" customWidth="1"/>
-    <col min="3" max="3" width="80" style="15" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="15"/>
+    <col min="1" max="1" width="6.140625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="21" style="11" customWidth="1"/>
+    <col min="3" max="3" width="80" style="11" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:3" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="35" t="s">
+        <v>600</v>
+      </c>
+      <c r="C2" s="34"/>
+    </row>
+    <row r="4" spans="2:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
+        <v>488</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="17" t="s">
+        <v>597</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>612</v>
       </c>
-      <c r="C2" s="17"/>
-    </row>
-    <row r="4" spans="2:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
+    </row>
+    <row r="19" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>613</v>
       </c>
-      <c r="C4" s="18" t="s">
+    </row>
+    <row r="20" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="20" t="s">
+    <row r="23" spans="2:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="36" t="s">
+        <v>603</v>
+      </c>
+      <c r="C23" s="34"/>
+    </row>
+    <row r="24" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="33" t="s">
+        <v>615</v>
+      </c>
+      <c r="C24" s="34"/>
+    </row>
+    <row r="25" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="33" t="s">
+        <v>616</v>
+      </c>
+      <c r="C25" s="34"/>
+    </row>
+    <row r="26" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="33" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="20" t="s">
+      <c r="C26" s="34"/>
+    </row>
+    <row r="27" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="33" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="20" t="s">
+      <c r="C27" s="34"/>
+    </row>
+    <row r="28" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="33" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
-        <v>497</v>
-      </c>
-      <c r="C8" s="20" t="s">
+      <c r="C28" s="34"/>
+    </row>
+    <row r="29" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="33" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="21" t="s">
-        <v>610</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
-        <v>609</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="25" t="s">
-        <v>615</v>
-      </c>
-      <c r="C23" s="17"/>
-    </row>
-    <row r="24" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="26" t="s">
-        <v>627</v>
-      </c>
-      <c r="C24" s="17"/>
-    </row>
-    <row r="25" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="26" t="s">
-        <v>628</v>
-      </c>
-      <c r="C25" s="17"/>
-    </row>
-    <row r="26" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="26" t="s">
-        <v>629</v>
-      </c>
-      <c r="C26" s="17"/>
-    </row>
-    <row r="27" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="26" t="s">
-        <v>630</v>
-      </c>
-      <c r="C27" s="17"/>
-    </row>
-    <row r="28" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="26" t="s">
-        <v>631</v>
-      </c>
-      <c r="C28" s="17"/>
-    </row>
-    <row r="29" spans="2:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="26" t="s">
-        <v>632</v>
-      </c>
-      <c r="C29" s="17"/>
+      <c r="C29" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="8">
